--- a/DEVELOPMENT_ALL_OLD_NEW/COLINSLOFT/CS.0229 - TOUCH LIGHT BLUE WASH.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/COLINSLOFT/CS.0229 - TOUCH LIGHT BLUE WASH.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\New Recipe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\TC.DEVELOPMENT.BRAND FILE 2\COLINSLOFT\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E934CF98-A679-42AE-8CEE-9E68B9F20675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SABLON" sheetId="1" r:id="rId1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
   <si>
     <t>dcr</t>
   </si>
@@ -243,12 +244,24 @@
   </si>
   <si>
     <t xml:space="preserve">EXTRACT &amp; DRYER </t>
+  </si>
+  <si>
+    <t>HAND SAND (400)</t>
+  </si>
+  <si>
+    <t>TM PLUS</t>
+  </si>
+  <si>
+    <t>ACTIVITOR</t>
+  </si>
+  <si>
+    <t>BROWN GGL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0.0000_);_(&quot;$&quot;* \(#,##0.0000\);_(&quot;$&quot;* &quot;-&quot;????_);_(@_)"/>
@@ -1767,188 +1780,251 @@
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="50" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="48" fillId="5" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1962,6 +2038,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -2040,8 +2122,116 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2052,24 +2242,6 @@
     <xf numFmtId="164" fontId="16" fillId="3" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2079,194 +2251,35 @@
     <xf numFmtId="164" fontId="8" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2274,97 +2287,97 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="5" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="50" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="49" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="49" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="55" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="56" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="50" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="53" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Currency 2 2" xfId="4"/>
+    <cellStyle name="Currency 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 3" xfId="1"/>
-    <cellStyle name="Normal 3 2" xfId="2"/>
-    <cellStyle name="Normal_0136" xfId="3"/>
+    <cellStyle name="Normal 2 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 3 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal_0136" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2380,7 +2393,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sayfa1"/>
@@ -2644,20 +2657,23 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="ALL SAMPLES"/>
       <sheetName val="Sheet1"/>
+      <sheetName val="DATA"/>
       <sheetName val="CUSTOMER"/>
-      <sheetName val="DATA"/>
       <sheetName val="SABLON"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
+      <sheetData sheetId="2">
         <row r="2">
           <cell r="B2" t="str">
             <v>BILAL</v>
@@ -2705,6 +2721,7 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
@@ -2973,7 +2990,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sayfa3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3772,21 +3789,21 @@
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="141">
+      <c r="C2" s="172">
         <v>46268</v>
       </c>
-      <c r="D2" s="142"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="141" t="s">
+      <c r="D2" s="173"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="142"/>
-      <c r="H2" s="144" t="s">
+      <c r="G2" s="173"/>
+      <c r="H2" s="175" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="145"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="146"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="177"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
@@ -3795,17 +3812,17 @@
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="141" t="s">
+      <c r="C3" s="172" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="142"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="153" t="s">
+      <c r="D3" s="173"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="154"/>
+      <c r="I3" s="185"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
       <c r="L3" s="4"/>
@@ -3819,17 +3836,17 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="155" t="s">
+      <c r="C4" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="156"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="150"/>
-      <c r="H4" s="158"/>
-      <c r="I4" s="159"/>
-      <c r="J4" s="158"/>
-      <c r="K4" s="159"/>
+      <c r="D4" s="187"/>
+      <c r="E4" s="188"/>
+      <c r="F4" s="180"/>
+      <c r="G4" s="181"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="189"/>
+      <c r="K4" s="190"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
@@ -3838,17 +3855,17 @@
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="160">
+      <c r="C5" s="191">
         <v>60552621</v>
       </c>
-      <c r="D5" s="161"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="149"/>
-      <c r="G5" s="150"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="111"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="193"/>
+      <c r="F5" s="180"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="170"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="170"/>
+      <c r="K5" s="171"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
@@ -3857,17 +3874,17 @@
       <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="135" t="s">
+      <c r="C6" s="194" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="136"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="150"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="111"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="196"/>
+      <c r="F6" s="180"/>
+      <c r="G6" s="181"/>
+      <c r="H6" s="170"/>
+      <c r="I6" s="171"/>
+      <c r="J6" s="170"/>
+      <c r="K6" s="171"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
@@ -3876,17 +3893,17 @@
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="138" t="s">
+      <c r="C7" s="167" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="139"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="149"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="111"/>
+      <c r="D7" s="168"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="180"/>
+      <c r="G7" s="181"/>
+      <c r="H7" s="170"/>
+      <c r="I7" s="171"/>
+      <c r="J7" s="170"/>
+      <c r="K7" s="171"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
@@ -3895,15 +3912,15 @@
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="129"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="131"/>
-      <c r="F8" s="149"/>
-      <c r="G8" s="150"/>
+      <c r="C8" s="197"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="199"/>
+      <c r="F8" s="180"/>
+      <c r="G8" s="181"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="111"/>
+      <c r="J8" s="170"/>
+      <c r="K8" s="171"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
@@ -3912,17 +3929,17 @@
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="132">
+      <c r="C9" s="200">
         <v>4</v>
       </c>
-      <c r="D9" s="133"/>
-      <c r="E9" s="134"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="150"/>
+      <c r="D9" s="201"/>
+      <c r="E9" s="202"/>
+      <c r="F9" s="180"/>
+      <c r="G9" s="181"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="111"/>
+      <c r="J9" s="170"/>
+      <c r="K9" s="171"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
@@ -3931,15 +3948,15 @@
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="132"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="149"/>
-      <c r="G10" s="150"/>
+      <c r="C10" s="200"/>
+      <c r="D10" s="201"/>
+      <c r="E10" s="202"/>
+      <c r="F10" s="180"/>
+      <c r="G10" s="181"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="111"/>
+      <c r="J10" s="170"/>
+      <c r="K10" s="171"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
@@ -3948,15 +3965,15 @@
       <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="107"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="109"/>
-      <c r="F11" s="149"/>
-      <c r="G11" s="150"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="111"/>
+      <c r="C11" s="203"/>
+      <c r="D11" s="204"/>
+      <c r="E11" s="205"/>
+      <c r="F11" s="180"/>
+      <c r="G11" s="181"/>
+      <c r="H11" s="170"/>
+      <c r="I11" s="171"/>
+      <c r="J11" s="170"/>
+      <c r="K11" s="171"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
@@ -3965,17 +3982,17 @@
       <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="126" t="s">
+      <c r="C12" s="206" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="127"/>
-      <c r="E12" s="128"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="111"/>
+      <c r="D12" s="207"/>
+      <c r="E12" s="208"/>
+      <c r="F12" s="180"/>
+      <c r="G12" s="181"/>
+      <c r="H12" s="170"/>
+      <c r="I12" s="171"/>
+      <c r="J12" s="170"/>
+      <c r="K12" s="171"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
@@ -3984,15 +4001,15 @@
       <c r="B13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="107"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="151"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="111"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="204"/>
+      <c r="E13" s="205"/>
+      <c r="F13" s="182"/>
+      <c r="G13" s="183"/>
+      <c r="H13" s="170"/>
+      <c r="I13" s="171"/>
+      <c r="J13" s="170"/>
+      <c r="K13" s="171"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -4001,17 +4018,17 @@
       <c r="B14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="112"/>
-      <c r="D14" s="112"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="114" t="s">
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
+      <c r="E14" s="210"/>
+      <c r="F14" s="211" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="115"/>
-      <c r="H14" s="118" t="s">
+      <c r="G14" s="212"/>
+      <c r="H14" s="215" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="119"/>
+      <c r="I14" s="216"/>
       <c r="J14" s="16"/>
       <c r="K14" s="17"/>
       <c r="L14" s="4"/>
@@ -4029,14 +4046,14 @@
       <c r="E15" s="21">
         <v>1</v>
       </c>
-      <c r="F15" s="116"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="116"/>
-      <c r="I15" s="120"/>
-      <c r="J15" s="121" t="s">
+      <c r="F15" s="213"/>
+      <c r="G15" s="214"/>
+      <c r="H15" s="213"/>
+      <c r="I15" s="217"/>
+      <c r="J15" s="218" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="123" t="s">
+      <c r="K15" s="220" t="s">
         <v>20</v>
       </c>
       <c r="L15" s="4"/>
@@ -4062,551 +4079,603 @@
       <c r="G16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="222" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="125"/>
-      <c r="J16" s="122"/>
-      <c r="K16" s="124"/>
+      <c r="I16" s="222"/>
+      <c r="J16" s="219"/>
+      <c r="K16" s="221"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
     </row>
     <row r="17" spans="1:13" ht="98.1" customHeight="1">
       <c r="A17" s="26"/>
-      <c r="B17" s="163" t="s">
+      <c r="B17" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="164" t="s">
+      <c r="C17" s="223" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="165"/>
-      <c r="E17" s="165"/>
-      <c r="F17" s="165"/>
-      <c r="G17" s="165"/>
-      <c r="H17" s="165"/>
-      <c r="I17" s="166"/>
-      <c r="J17" s="167"/>
-      <c r="K17" s="168"/>
+      <c r="D17" s="224"/>
+      <c r="E17" s="224"/>
+      <c r="F17" s="224"/>
+      <c r="G17" s="224"/>
+      <c r="H17" s="224"/>
+      <c r="I17" s="225"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="87"/>
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
     </row>
     <row r="18" spans="1:13" ht="98.1" customHeight="1">
       <c r="A18" s="26"/>
-      <c r="B18" s="163" t="s">
+      <c r="B18" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="169"/>
-      <c r="D18" s="170"/>
-      <c r="E18" s="170"/>
-      <c r="F18" s="170"/>
-      <c r="G18" s="170"/>
-      <c r="H18" s="170"/>
-      <c r="I18" s="171"/>
-      <c r="J18" s="167"/>
-      <c r="K18" s="168"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="86"/>
+      <c r="K18" s="87"/>
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
     </row>
-    <row r="19" spans="1:13" ht="74.099999999999994" customHeight="1">
+    <row r="19" spans="1:13" ht="98.1" customHeight="1">
       <c r="A19" s="26"/>
-      <c r="B19" s="172"/>
-      <c r="C19" s="173"/>
-      <c r="D19" s="174"/>
-      <c r="E19" s="174"/>
-      <c r="F19" s="174"/>
-      <c r="G19" s="174"/>
-      <c r="H19" s="174"/>
-      <c r="I19" s="175"/>
-      <c r="J19" s="176"/>
-      <c r="K19" s="177"/>
+      <c r="B19" s="268" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="88"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="35"/>
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
     </row>
     <row r="20" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A20" s="26"/>
-      <c r="B20" s="178" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="179">
-        <v>10</v>
-      </c>
-      <c r="D20" s="179">
-        <v>50</v>
-      </c>
-      <c r="E20" s="179"/>
-      <c r="F20" s="179">
-        <v>2</v>
-      </c>
-      <c r="G20" s="180" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" s="181" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" s="182"/>
-      <c r="J20" s="167"/>
-      <c r="K20" s="168"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="226"/>
+      <c r="D20" s="227"/>
+      <c r="E20" s="227"/>
+      <c r="F20" s="227"/>
+      <c r="G20" s="227"/>
+      <c r="H20" s="227"/>
+      <c r="I20" s="228"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="93"/>
       <c r="L20" s="25"/>
       <c r="M20" s="25"/>
     </row>
     <row r="21" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A21" s="26"/>
-      <c r="B21" s="183" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="184">
-        <v>1</v>
-      </c>
-      <c r="D21" s="184" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="179"/>
-      <c r="F21" s="179">
+      <c r="B21" s="94" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="95">
+        <v>10</v>
+      </c>
+      <c r="D21" s="95">
+        <v>50</v>
+      </c>
+      <c r="E21" s="95">
+        <v>120</v>
+      </c>
+      <c r="F21" s="95">
         <v>2</v>
       </c>
-      <c r="G21" s="180" t="s">
+      <c r="G21" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="181" t="s">
-        <v>41</v>
-      </c>
-      <c r="I21" s="182"/>
-      <c r="J21" s="167"/>
-      <c r="K21" s="168"/>
+      <c r="H21" s="229" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" s="230"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="87"/>
       <c r="L21" s="25"/>
       <c r="M21" s="25"/>
     </row>
     <row r="22" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A22" s="26"/>
-      <c r="B22" s="185"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="186"/>
-      <c r="E22" s="186"/>
-      <c r="F22" s="187"/>
-      <c r="G22" s="187"/>
-      <c r="H22" s="188"/>
-      <c r="I22" s="188"/>
-      <c r="J22" s="189"/>
-      <c r="K22" s="189"/>
+      <c r="B22" s="99" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="100">
+        <v>1</v>
+      </c>
+      <c r="D22" s="100" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="95">
+        <v>150</v>
+      </c>
+      <c r="F22" s="95">
+        <v>2</v>
+      </c>
+      <c r="G22" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="229" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="230"/>
+      <c r="J22" s="86"/>
+      <c r="K22" s="87"/>
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
     </row>
     <row r="23" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A23" s="26"/>
-      <c r="B23" s="190" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="180">
-        <v>40</v>
-      </c>
-      <c r="D23" s="180">
-        <v>40</v>
-      </c>
-      <c r="E23" s="180"/>
-      <c r="F23" s="191">
-        <v>4</v>
-      </c>
-      <c r="G23" s="192" t="s">
-        <v>37</v>
-      </c>
-      <c r="H23" s="193" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" s="193"/>
-      <c r="J23" s="194"/>
-      <c r="K23" s="194"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="231"/>
+      <c r="I23" s="231"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
       <c r="L23" s="25"/>
       <c r="M23" s="25"/>
     </row>
     <row r="24" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A24" s="26"/>
-      <c r="B24" s="195"/>
-      <c r="C24" s="180"/>
-      <c r="D24" s="180"/>
-      <c r="E24" s="180"/>
-      <c r="F24" s="194">
-        <v>1</v>
-      </c>
-      <c r="G24" s="180" t="s">
+      <c r="B24" s="105" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="96">
+        <v>20</v>
+      </c>
+      <c r="D24" s="96">
+        <v>40</v>
+      </c>
+      <c r="E24" s="96"/>
+      <c r="F24" s="106">
+        <v>4</v>
+      </c>
+      <c r="G24" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="196" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" s="196"/>
-      <c r="J24" s="194"/>
-      <c r="K24" s="194"/>
+      <c r="H24" s="234" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="234"/>
+      <c r="J24" s="108"/>
+      <c r="K24" s="108"/>
       <c r="L24" s="25"/>
       <c r="M24" s="25"/>
     </row>
     <row r="25" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A25" s="26"/>
-      <c r="B25" s="195"/>
-      <c r="C25" s="180"/>
-      <c r="D25" s="180"/>
-      <c r="E25" s="180"/>
-      <c r="F25" s="191">
-        <v>5</v>
-      </c>
-      <c r="G25" s="191" t="s">
-        <v>45</v>
-      </c>
-      <c r="H25" s="197" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="198"/>
-      <c r="J25" s="194"/>
-      <c r="K25" s="194"/>
+      <c r="B25" s="109"/>
+      <c r="C25" s="96"/>
+      <c r="D25" s="96"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="108">
+        <v>1</v>
+      </c>
+      <c r="G25" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="235" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" s="235"/>
+      <c r="J25" s="108"/>
+      <c r="K25" s="108"/>
       <c r="L25" s="25"/>
       <c r="M25" s="25"/>
     </row>
     <row r="26" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A26" s="26"/>
-      <c r="B26" s="195" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="180">
-        <v>3</v>
-      </c>
-      <c r="D26" s="180" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="199"/>
-      <c r="F26" s="200">
+      <c r="B26" s="109"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="106">
         <v>5</v>
       </c>
-      <c r="G26" s="201" t="s">
+      <c r="G26" s="106" t="s">
         <v>45</v>
       </c>
-      <c r="H26" s="202" t="s">
-        <v>48</v>
-      </c>
-      <c r="I26" s="202"/>
-      <c r="J26" s="194"/>
-      <c r="K26" s="194"/>
+      <c r="H26" s="237" t="s">
+        <v>46</v>
+      </c>
+      <c r="I26" s="238"/>
+      <c r="J26" s="108"/>
+      <c r="K26" s="108"/>
       <c r="L26" s="25"/>
       <c r="M26" s="25"/>
     </row>
     <row r="27" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A27" s="26"/>
-      <c r="B27" s="178"/>
-      <c r="C27" s="179"/>
-      <c r="D27" s="179"/>
-      <c r="E27" s="179"/>
-      <c r="F27" s="180"/>
-      <c r="G27" s="180"/>
-      <c r="H27" s="203"/>
-      <c r="I27" s="204"/>
-      <c r="J27" s="167"/>
-      <c r="K27" s="168"/>
+      <c r="B27" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="96">
+        <v>3</v>
+      </c>
+      <c r="D27" s="96" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="110">
+        <v>200</v>
+      </c>
+      <c r="F27" s="111">
+        <v>5</v>
+      </c>
+      <c r="G27" s="112" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="236" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" s="236"/>
+      <c r="J27" s="108"/>
+      <c r="K27" s="108"/>
       <c r="L27" s="25"/>
       <c r="M27" s="25"/>
     </row>
     <row r="28" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A28" s="26"/>
-      <c r="B28" s="216"/>
-      <c r="C28" s="217"/>
-      <c r="D28" s="217"/>
-      <c r="E28" s="217"/>
-      <c r="F28" s="218"/>
-      <c r="G28" s="218"/>
-      <c r="H28" s="216"/>
-      <c r="I28" s="216"/>
-      <c r="J28" s="218"/>
-      <c r="K28" s="218"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="95"/>
+      <c r="E28" s="95"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="96"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="98"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="87"/>
       <c r="L28" s="25"/>
       <c r="M28" s="25"/>
     </row>
     <row r="29" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A29" s="26"/>
-      <c r="B29" s="178" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="219"/>
-      <c r="D29" s="219" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="219"/>
-      <c r="F29" s="220"/>
-      <c r="G29" s="221" t="s">
-        <v>37</v>
-      </c>
-      <c r="H29" s="222" t="s">
-        <v>52</v>
-      </c>
-      <c r="I29" s="223"/>
-      <c r="J29" s="220"/>
-      <c r="K29" s="220"/>
+      <c r="B29" s="120"/>
+      <c r="C29" s="121"/>
+      <c r="D29" s="121"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="122"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="120"/>
+      <c r="I29" s="120"/>
+      <c r="J29" s="122"/>
+      <c r="K29" s="122"/>
       <c r="L29" s="25"/>
       <c r="M29" s="25"/>
     </row>
     <row r="30" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A30" s="26"/>
-      <c r="B30" s="224" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="225">
-        <v>2</v>
-      </c>
-      <c r="D30" s="225" t="s">
+      <c r="B30" s="94" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="123">
+        <v>10</v>
+      </c>
+      <c r="D30" s="123" t="s">
         <v>40</v>
       </c>
-      <c r="E30" s="225"/>
-      <c r="F30" s="220"/>
-      <c r="G30" s="221" t="s">
-        <v>37</v>
-      </c>
-      <c r="H30" s="222" t="s">
-        <v>56</v>
-      </c>
-      <c r="I30" s="223"/>
-      <c r="J30" s="220"/>
-      <c r="K30" s="220"/>
+      <c r="E30" s="123">
+        <v>100</v>
+      </c>
+      <c r="F30" s="124">
+        <v>6</v>
+      </c>
+      <c r="G30" s="125" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="232" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30" s="233"/>
+      <c r="J30" s="124"/>
+      <c r="K30" s="124"/>
       <c r="L30" s="25"/>
       <c r="M30" s="25"/>
     </row>
     <row r="31" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A31" s="26"/>
-      <c r="B31" s="226"/>
-      <c r="C31" s="227"/>
-      <c r="D31" s="227"/>
-      <c r="E31" s="227"/>
-      <c r="F31" s="189"/>
-      <c r="G31" s="228"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="230"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="189"/>
+      <c r="B31" s="127" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="128">
+        <v>2</v>
+      </c>
+      <c r="D31" s="128" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="128">
+        <v>150</v>
+      </c>
+      <c r="F31" s="124">
+        <v>200</v>
+      </c>
+      <c r="G31" s="125" t="s">
+        <v>37</v>
+      </c>
+      <c r="H31" s="232" t="s">
+        <v>56</v>
+      </c>
+      <c r="I31" s="233"/>
+      <c r="J31" s="124"/>
+      <c r="K31" s="124"/>
       <c r="L31" s="25"/>
       <c r="M31" s="25"/>
     </row>
     <row r="32" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A32" s="26"/>
-      <c r="B32" s="190" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="179"/>
-      <c r="D32" s="179"/>
-      <c r="E32" s="179"/>
-      <c r="F32" s="212"/>
-      <c r="G32" s="231" t="s">
-        <v>37</v>
-      </c>
-      <c r="H32" s="232" t="s">
-        <v>58</v>
-      </c>
-      <c r="I32" s="233"/>
-      <c r="J32" s="168"/>
-      <c r="K32" s="168"/>
+      <c r="B32" s="129"/>
+      <c r="C32" s="130"/>
+      <c r="D32" s="130"/>
+      <c r="E32" s="130"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="131"/>
+      <c r="H32" s="132"/>
+      <c r="I32" s="133"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
       <c r="L32" s="25"/>
       <c r="M32" s="25"/>
     </row>
     <row r="33" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A33" s="26"/>
-      <c r="B33" s="234" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="235">
-        <v>2</v>
-      </c>
-      <c r="D33" s="236" t="s">
+      <c r="B33" s="105" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="95">
+        <v>3</v>
+      </c>
+      <c r="D33" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="235"/>
-      <c r="F33" s="212"/>
-      <c r="G33" s="212"/>
-      <c r="H33" s="214"/>
-      <c r="I33" s="214"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
+      <c r="E33" s="95">
+        <v>100</v>
+      </c>
+      <c r="F33" s="117">
+        <v>100</v>
+      </c>
+      <c r="G33" s="134" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="165" t="s">
+        <v>58</v>
+      </c>
+      <c r="I33" s="166"/>
+      <c r="J33" s="87"/>
+      <c r="K33" s="87"/>
       <c r="L33" s="25"/>
       <c r="M33" s="25"/>
     </row>
     <row r="34" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A34" s="26"/>
-      <c r="B34" s="205"/>
-      <c r="C34" s="206" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="207"/>
-      <c r="E34" s="207"/>
-      <c r="F34" s="207"/>
-      <c r="G34" s="208"/>
-      <c r="H34" s="209"/>
-      <c r="I34" s="210"/>
-      <c r="J34" s="189"/>
-      <c r="K34" s="211"/>
+      <c r="B34" s="135" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="136">
+        <v>2</v>
+      </c>
+      <c r="D34" s="137" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="136">
+        <v>200</v>
+      </c>
+      <c r="F34" s="117">
+        <v>50</v>
+      </c>
+      <c r="G34" s="134" t="s">
+        <v>37</v>
+      </c>
+      <c r="H34" s="158" t="s">
+        <v>69</v>
+      </c>
+      <c r="I34" s="158"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
     </row>
     <row r="35" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A35" s="26"/>
-      <c r="B35" s="190" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="179"/>
-      <c r="D35" s="179"/>
-      <c r="E35" s="179"/>
-      <c r="F35" s="212"/>
-      <c r="G35" s="213" t="s">
-        <v>37</v>
-      </c>
-      <c r="H35" s="214" t="s">
-        <v>51</v>
-      </c>
-      <c r="I35" s="214"/>
-      <c r="J35" s="212"/>
-      <c r="K35" s="212"/>
+      <c r="B35" s="113"/>
+      <c r="C35" s="155" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="156"/>
+      <c r="E35" s="156"/>
+      <c r="F35" s="156"/>
+      <c r="G35" s="157"/>
+      <c r="H35" s="114"/>
+      <c r="I35" s="115"/>
+      <c r="J35" s="104"/>
+      <c r="K35" s="116"/>
       <c r="L35" s="25"/>
       <c r="M35" s="25"/>
     </row>
     <row r="36" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A36" s="26"/>
-      <c r="B36" s="190"/>
-      <c r="C36" s="179"/>
-      <c r="D36" s="179"/>
-      <c r="E36" s="179"/>
-      <c r="F36" s="212"/>
-      <c r="G36" s="213" t="s">
+      <c r="B36" s="105" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="95"/>
+      <c r="D36" s="95"/>
+      <c r="E36" s="95"/>
+      <c r="F36" s="117">
+        <v>5</v>
+      </c>
+      <c r="G36" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="H36" s="214" t="s">
-        <v>52</v>
-      </c>
-      <c r="I36" s="214"/>
-      <c r="J36" s="212"/>
-      <c r="K36" s="212"/>
+      <c r="H36" s="158" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" s="158"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="117"/>
       <c r="L36" s="25"/>
       <c r="M36" s="25"/>
     </row>
     <row r="37" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A37" s="26"/>
-      <c r="B37" s="215"/>
-      <c r="C37" s="179"/>
-      <c r="D37" s="179"/>
-      <c r="E37" s="179"/>
-      <c r="F37" s="212"/>
-      <c r="G37" s="213" t="s">
+      <c r="B37" s="105"/>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="117">
+        <v>5</v>
+      </c>
+      <c r="G37" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="214" t="s">
-        <v>53</v>
-      </c>
-      <c r="I37" s="214"/>
-      <c r="J37" s="212"/>
-      <c r="K37" s="212"/>
+      <c r="H37" s="158" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" s="158"/>
+      <c r="J37" s="117"/>
+      <c r="K37" s="117"/>
       <c r="L37" s="25"/>
       <c r="M37" s="25"/>
     </row>
     <row r="38" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A38" s="26"/>
-      <c r="B38" s="226"/>
-      <c r="C38" s="227"/>
-      <c r="D38" s="227"/>
-      <c r="E38" s="227"/>
-      <c r="F38" s="189"/>
-      <c r="G38" s="228"/>
-      <c r="H38" s="229"/>
-      <c r="I38" s="230"/>
-      <c r="J38" s="189"/>
-      <c r="K38" s="189"/>
+      <c r="B38" s="119"/>
+      <c r="C38" s="95"/>
+      <c r="D38" s="95"/>
+      <c r="E38" s="95"/>
+      <c r="F38" s="117">
+        <v>900</v>
+      </c>
+      <c r="G38" s="118" t="s">
+        <v>37</v>
+      </c>
+      <c r="H38" s="158" t="s">
+        <v>53</v>
+      </c>
+      <c r="I38" s="158"/>
+      <c r="J38" s="117"/>
+      <c r="K38" s="117"/>
       <c r="L38" s="25"/>
       <c r="M38" s="25"/>
     </row>
     <row r="39" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A39" s="26"/>
-      <c r="B39" s="190" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="179"/>
-      <c r="D39" s="179"/>
-      <c r="E39" s="179"/>
-      <c r="F39" s="212"/>
-      <c r="G39" s="231" t="s">
-        <v>37</v>
-      </c>
-      <c r="H39" s="232" t="s">
-        <v>58</v>
-      </c>
-      <c r="I39" s="233"/>
-      <c r="J39" s="168"/>
-      <c r="K39" s="168"/>
+      <c r="B39" s="129"/>
+      <c r="C39" s="130"/>
+      <c r="D39" s="130"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="131"/>
+      <c r="H39" s="132"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="104"/>
+      <c r="K39" s="104"/>
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
     </row>
     <row r="40" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A40" s="26"/>
-      <c r="B40" s="234" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" s="235">
+      <c r="B40" s="105" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="95">
         <v>2</v>
       </c>
-      <c r="D40" s="236" t="s">
+      <c r="D40" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="E40" s="235"/>
-      <c r="F40" s="212"/>
-      <c r="G40" s="212"/>
-      <c r="H40" s="214"/>
-      <c r="I40" s="214"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
+      <c r="E40" s="95">
+        <v>100</v>
+      </c>
+      <c r="F40" s="117">
+        <v>100</v>
+      </c>
+      <c r="G40" s="134" t="s">
+        <v>37</v>
+      </c>
+      <c r="H40" s="165" t="s">
+        <v>58</v>
+      </c>
+      <c r="I40" s="166"/>
+      <c r="J40" s="87"/>
+      <c r="K40" s="87"/>
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
     </row>
     <row r="41" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A41" s="26"/>
-      <c r="B41" s="205"/>
-      <c r="C41" s="227"/>
-      <c r="D41" s="227"/>
-      <c r="E41" s="227"/>
-      <c r="F41" s="189"/>
-      <c r="G41" s="189"/>
-      <c r="H41" s="209"/>
-      <c r="I41" s="210"/>
-      <c r="J41" s="189"/>
-      <c r="K41" s="211"/>
+      <c r="B41" s="135" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="136">
+        <v>2</v>
+      </c>
+      <c r="D41" s="137" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" s="136">
+        <v>150</v>
+      </c>
+      <c r="F41" s="117"/>
+      <c r="G41" s="117"/>
+      <c r="H41" s="158"/>
+      <c r="I41" s="158"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
       <c r="L41" s="25"/>
       <c r="M41" s="25"/>
     </row>
     <row r="42" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A42" s="26"/>
-      <c r="B42" s="237" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="236"/>
-      <c r="D42" s="236">
-        <v>45</v>
-      </c>
-      <c r="E42" s="236"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="H42" s="238" t="s">
-        <v>60</v>
-      </c>
-      <c r="I42" s="238"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
+      <c r="B42" s="113"/>
+      <c r="C42" s="130"/>
+      <c r="D42" s="130"/>
+      <c r="E42" s="130"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="114"/>
+      <c r="I42" s="115"/>
+      <c r="J42" s="104"/>
+      <c r="K42" s="116"/>
       <c r="L42" s="25"/>
       <c r="M42" s="25"/>
     </row>
     <row r="43" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A43" s="26"/>
-      <c r="B43" s="237"/>
-      <c r="C43" s="236"/>
-      <c r="D43" s="236"/>
-      <c r="E43" s="236"/>
-      <c r="F43" s="28"/>
+      <c r="B43" s="138" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="137">
+        <v>5</v>
+      </c>
+      <c r="D43" s="137">
+        <v>45</v>
+      </c>
+      <c r="E43" s="137">
+        <v>100</v>
+      </c>
+      <c r="F43" s="28">
+        <v>2</v>
+      </c>
       <c r="G43" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="H43" s="239" t="s">
-        <v>61</v>
-      </c>
-      <c r="I43" s="239"/>
+      <c r="H43" s="159" t="s">
+        <v>60</v>
+      </c>
+      <c r="I43" s="159"/>
       <c r="J43" s="28"/>
       <c r="K43" s="28"/>
       <c r="L43" s="25"/>
@@ -4614,196 +4683,218 @@
     </row>
     <row r="44" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A44" s="26"/>
-      <c r="B44" s="190" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" s="179">
-        <v>2</v>
-      </c>
-      <c r="D44" s="179" t="s">
-        <v>40</v>
-      </c>
-      <c r="E44" s="179"/>
-      <c r="F44" s="168"/>
-      <c r="G44" s="168"/>
-      <c r="H44" s="240"/>
-      <c r="I44" s="240"/>
-      <c r="J44" s="168"/>
-      <c r="K44" s="168"/>
+      <c r="B44" s="138"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="137"/>
+      <c r="E44" s="137"/>
+      <c r="F44" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="G44" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="H44" s="239" t="s">
+        <v>61</v>
+      </c>
+      <c r="I44" s="239"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="28"/>
       <c r="L44" s="25"/>
       <c r="M44" s="25"/>
     </row>
     <row r="45" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A45" s="26"/>
-      <c r="B45" s="205"/>
-      <c r="C45" s="241"/>
-      <c r="D45" s="242"/>
-      <c r="E45" s="242"/>
-      <c r="F45" s="242"/>
-      <c r="G45" s="243"/>
-      <c r="H45" s="244"/>
-      <c r="I45" s="245"/>
-      <c r="J45" s="246"/>
-      <c r="K45" s="246"/>
+      <c r="B45" s="105" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="95">
+        <v>2</v>
+      </c>
+      <c r="D45" s="95" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" s="95">
+        <v>150</v>
+      </c>
+      <c r="F45" s="87"/>
+      <c r="G45" s="87"/>
+      <c r="H45" s="240"/>
+      <c r="I45" s="240"/>
+      <c r="J45" s="87"/>
+      <c r="K45" s="87"/>
       <c r="L45" s="25"/>
       <c r="M45" s="25"/>
     </row>
     <row r="46" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A46" s="26"/>
-      <c r="B46" s="247" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46" s="219"/>
-      <c r="D46" s="219">
-        <v>45</v>
-      </c>
-      <c r="E46" s="219"/>
-      <c r="F46" s="220"/>
-      <c r="G46" s="212" t="s">
-        <v>63</v>
-      </c>
-      <c r="H46" s="222"/>
-      <c r="I46" s="223"/>
-      <c r="J46" s="220"/>
-      <c r="K46" s="248"/>
+      <c r="B46" s="113"/>
+      <c r="C46" s="160"/>
+      <c r="D46" s="161"/>
+      <c r="E46" s="161"/>
+      <c r="F46" s="161"/>
+      <c r="G46" s="162"/>
+      <c r="H46" s="163"/>
+      <c r="I46" s="164"/>
+      <c r="J46" s="139"/>
+      <c r="K46" s="139"/>
       <c r="L46" s="25"/>
       <c r="M46" s="25"/>
     </row>
     <row r="47" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A47" s="26"/>
-      <c r="B47" s="247"/>
-      <c r="C47" s="219"/>
-      <c r="D47" s="219"/>
-      <c r="E47" s="219"/>
-      <c r="F47" s="220"/>
-      <c r="G47" s="212" t="s">
+      <c r="B47" s="140" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" s="123">
+        <v>2</v>
+      </c>
+      <c r="D47" s="123">
+        <v>45</v>
+      </c>
+      <c r="E47" s="123">
+        <v>80</v>
+      </c>
+      <c r="F47" s="124">
+        <v>2</v>
+      </c>
+      <c r="G47" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="H47" s="249"/>
-      <c r="I47" s="250"/>
-      <c r="J47" s="220"/>
-      <c r="K47" s="248"/>
+      <c r="H47" s="232" t="s">
+        <v>71</v>
+      </c>
+      <c r="I47" s="233"/>
+      <c r="J47" s="124"/>
+      <c r="K47" s="141"/>
       <c r="L47" s="25"/>
       <c r="M47" s="25"/>
     </row>
     <row r="48" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A48" s="26"/>
-      <c r="B48" s="247" t="s">
+      <c r="B48" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="219"/>
-      <c r="D48" s="219"/>
-      <c r="E48" s="219"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="212" t="s">
+      <c r="C48" s="123"/>
+      <c r="D48" s="123"/>
+      <c r="E48" s="123"/>
+      <c r="F48" s="124">
+        <v>100</v>
+      </c>
+      <c r="G48" s="117" t="s">
         <v>37</v>
       </c>
-      <c r="H48" s="249" t="s">
+      <c r="H48" s="126" t="s">
         <v>64</v>
       </c>
-      <c r="I48" s="221"/>
-      <c r="J48" s="220"/>
-      <c r="K48" s="248"/>
+      <c r="I48" s="125"/>
+      <c r="J48" s="124"/>
+      <c r="K48" s="141"/>
       <c r="L48" s="25"/>
       <c r="M48" s="25"/>
     </row>
     <row r="49" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A49" s="26"/>
-      <c r="B49" s="251"/>
-      <c r="C49" s="252"/>
-      <c r="D49" s="253"/>
-      <c r="E49" s="253"/>
-      <c r="F49" s="254"/>
-      <c r="G49" s="254"/>
-      <c r="H49" s="255"/>
-      <c r="I49" s="255"/>
-      <c r="J49" s="254"/>
-      <c r="K49" s="254"/>
+      <c r="B49" s="142"/>
+      <c r="C49" s="143"/>
+      <c r="D49" s="247"/>
+      <c r="E49" s="247"/>
+      <c r="F49" s="144"/>
+      <c r="G49" s="144"/>
+      <c r="H49" s="243"/>
+      <c r="I49" s="243"/>
+      <c r="J49" s="144"/>
+      <c r="K49" s="144"/>
       <c r="L49" s="25"/>
       <c r="M49" s="25"/>
     </row>
     <row r="50" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A50" s="26"/>
-      <c r="B50" s="256" t="s">
+      <c r="B50" s="145" t="s">
         <v>65</v>
       </c>
-      <c r="C50" s="257"/>
-      <c r="D50" s="258" t="s">
+      <c r="C50" s="146">
+        <v>2</v>
+      </c>
+      <c r="D50" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="258"/>
-      <c r="F50" s="259"/>
-      <c r="G50" s="213" t="s">
+      <c r="E50" s="147">
+        <v>100</v>
+      </c>
+      <c r="F50" s="148">
+        <v>4</v>
+      </c>
+      <c r="G50" s="118" t="s">
         <v>45</v>
       </c>
-      <c r="H50" s="260" t="s">
+      <c r="H50" s="244" t="s">
         <v>66</v>
       </c>
-      <c r="I50" s="260"/>
-      <c r="J50" s="194"/>
-      <c r="K50" s="261"/>
+      <c r="I50" s="244"/>
+      <c r="J50" s="108"/>
+      <c r="K50" s="149"/>
       <c r="L50" s="25"/>
       <c r="M50" s="25"/>
     </row>
     <row r="51" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A51" s="26"/>
-      <c r="B51" s="195" t="s">
+      <c r="B51" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="194"/>
-      <c r="D51" s="194"/>
-      <c r="E51" s="194"/>
-      <c r="F51" s="262"/>
-      <c r="G51" s="261"/>
-      <c r="H51" s="263"/>
-      <c r="I51" s="263"/>
-      <c r="J51" s="194"/>
-      <c r="K51" s="194"/>
+      <c r="C51" s="108"/>
+      <c r="D51" s="108"/>
+      <c r="E51" s="108"/>
+      <c r="F51" s="150"/>
+      <c r="G51" s="149"/>
+      <c r="H51" s="245"/>
+      <c r="I51" s="245"/>
+      <c r="J51" s="108"/>
+      <c r="K51" s="108"/>
       <c r="L51" s="25"/>
       <c r="M51" s="25"/>
     </row>
     <row r="52" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A52" s="26"/>
-      <c r="B52" s="264"/>
-      <c r="C52" s="265"/>
-      <c r="D52" s="265"/>
-      <c r="E52" s="265"/>
-      <c r="F52" s="266"/>
-      <c r="G52" s="266"/>
-      <c r="H52" s="267"/>
-      <c r="I52" s="267"/>
-      <c r="J52" s="266"/>
-      <c r="K52" s="266"/>
+      <c r="B52" s="151"/>
+      <c r="C52" s="152"/>
+      <c r="D52" s="152"/>
+      <c r="E52" s="152"/>
+      <c r="F52" s="153"/>
+      <c r="G52" s="153"/>
+      <c r="H52" s="246"/>
+      <c r="I52" s="246"/>
+      <c r="J52" s="153"/>
+      <c r="K52" s="153"/>
       <c r="L52" s="25"/>
       <c r="M52" s="25"/>
     </row>
     <row r="53" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A53" s="26"/>
-      <c r="B53" s="268"/>
-      <c r="C53" s="168"/>
-      <c r="D53" s="168"/>
-      <c r="E53" s="179"/>
-      <c r="F53" s="212"/>
-      <c r="G53" s="213"/>
-      <c r="H53" s="214"/>
-      <c r="I53" s="214"/>
-      <c r="J53" s="212"/>
-      <c r="K53" s="212"/>
+      <c r="B53" s="154"/>
+      <c r="C53" s="87"/>
+      <c r="D53" s="87"/>
+      <c r="E53" s="95"/>
+      <c r="F53" s="117"/>
+      <c r="G53" s="118"/>
+      <c r="H53" s="158"/>
+      <c r="I53" s="158"/>
+      <c r="J53" s="117"/>
+      <c r="K53" s="117"/>
       <c r="L53" s="25"/>
       <c r="M53" s="25"/>
     </row>
     <row r="54" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A54" s="26"/>
-      <c r="B54" s="268"/>
-      <c r="C54" s="168"/>
-      <c r="D54" s="168"/>
-      <c r="E54" s="179"/>
-      <c r="F54" s="212"/>
-      <c r="G54" s="213"/>
-      <c r="H54" s="214"/>
-      <c r="I54" s="214"/>
-      <c r="J54" s="212"/>
-      <c r="K54" s="212"/>
+      <c r="B54" s="154"/>
+      <c r="C54" s="87"/>
+      <c r="D54" s="87"/>
+      <c r="E54" s="95"/>
+      <c r="F54" s="117"/>
+      <c r="G54" s="118"/>
+      <c r="H54" s="158"/>
+      <c r="I54" s="158"/>
+      <c r="J54" s="117"/>
+      <c r="K54" s="117"/>
       <c r="L54" s="25"/>
       <c r="M54" s="25"/>
     </row>
@@ -4815,8 +4906,8 @@
       <c r="E55" s="35"/>
       <c r="F55" s="38"/>
       <c r="G55" s="38"/>
-      <c r="H55" s="103"/>
-      <c r="I55" s="104"/>
+      <c r="H55" s="248"/>
+      <c r="I55" s="249"/>
       <c r="J55" s="39"/>
       <c r="K55" s="35"/>
       <c r="L55" s="25"/>
@@ -4830,8 +4921,8 @@
       <c r="E56" s="35"/>
       <c r="F56" s="38"/>
       <c r="G56" s="38"/>
-      <c r="H56" s="103"/>
-      <c r="I56" s="104"/>
+      <c r="H56" s="248"/>
+      <c r="I56" s="249"/>
       <c r="J56" s="39"/>
       <c r="K56" s="35"/>
       <c r="L56" s="25"/>
@@ -4845,8 +4936,8 @@
       <c r="E57" s="35"/>
       <c r="F57" s="35"/>
       <c r="G57" s="42"/>
-      <c r="H57" s="105"/>
-      <c r="I57" s="106"/>
+      <c r="H57" s="241"/>
+      <c r="I57" s="242"/>
       <c r="J57" s="39"/>
       <c r="K57" s="35"/>
       <c r="L57" s="25"/>
@@ -4875,8 +4966,8 @@
       <c r="E59" s="33"/>
       <c r="F59" s="31"/>
       <c r="G59" s="34"/>
-      <c r="H59" s="97"/>
-      <c r="I59" s="97"/>
+      <c r="H59" s="251"/>
+      <c r="I59" s="251"/>
       <c r="J59" s="35"/>
       <c r="K59" s="35"/>
       <c r="L59" s="25"/>
@@ -4890,8 +4981,8 @@
       <c r="E60" s="33"/>
       <c r="F60" s="35"/>
       <c r="G60" s="35"/>
-      <c r="H60" s="98"/>
-      <c r="I60" s="98"/>
+      <c r="H60" s="252"/>
+      <c r="I60" s="252"/>
       <c r="J60" s="35"/>
       <c r="K60" s="35"/>
       <c r="L60" s="25"/>
@@ -4920,8 +5011,8 @@
       <c r="E62" s="33"/>
       <c r="F62" s="31"/>
       <c r="G62" s="31"/>
-      <c r="H62" s="99"/>
-      <c r="I62" s="99"/>
+      <c r="H62" s="253"/>
+      <c r="I62" s="253"/>
       <c r="J62" s="31"/>
       <c r="K62" s="31"/>
       <c r="L62" s="4"/>
@@ -4935,8 +5026,8 @@
       <c r="E63" s="33"/>
       <c r="F63" s="31"/>
       <c r="G63" s="31"/>
-      <c r="H63" s="99"/>
-      <c r="I63" s="99"/>
+      <c r="H63" s="253"/>
+      <c r="I63" s="253"/>
       <c r="J63" s="31"/>
       <c r="K63" s="31"/>
       <c r="L63" s="4"/>
@@ -4950,8 +5041,8 @@
       <c r="E64" s="44"/>
       <c r="F64" s="45"/>
       <c r="G64" s="45"/>
-      <c r="H64" s="100"/>
-      <c r="I64" s="101"/>
+      <c r="H64" s="254"/>
+      <c r="I64" s="255"/>
       <c r="J64" s="45"/>
       <c r="K64" s="56"/>
       <c r="L64" s="4"/>
@@ -4965,8 +5056,8 @@
       <c r="E65" s="58"/>
       <c r="F65" s="42"/>
       <c r="G65" s="42"/>
-      <c r="H65" s="102"/>
-      <c r="I65" s="102"/>
+      <c r="H65" s="256"/>
+      <c r="I65" s="256"/>
       <c r="J65" s="42"/>
       <c r="K65" s="42"/>
       <c r="L65" s="4"/>
@@ -4980,8 +5071,8 @@
       <c r="E66" s="58"/>
       <c r="F66" s="42"/>
       <c r="G66" s="42"/>
-      <c r="H66" s="91"/>
-      <c r="I66" s="91"/>
+      <c r="H66" s="257"/>
+      <c r="I66" s="257"/>
       <c r="J66" s="42"/>
       <c r="K66" s="42"/>
       <c r="L66" s="4"/>
@@ -4995,8 +5086,8 @@
       <c r="E67" s="33"/>
       <c r="F67" s="35"/>
       <c r="G67" s="35"/>
-      <c r="H67" s="92"/>
-      <c r="I67" s="92"/>
+      <c r="H67" s="258"/>
+      <c r="I67" s="258"/>
       <c r="J67" s="35"/>
       <c r="K67" s="35"/>
       <c r="L67" s="4"/>
@@ -5025,8 +5116,8 @@
       <c r="E69" s="33"/>
       <c r="F69" s="35"/>
       <c r="G69" s="35"/>
-      <c r="H69" s="93"/>
-      <c r="I69" s="94"/>
+      <c r="H69" s="259"/>
+      <c r="I69" s="260"/>
       <c r="J69" s="35"/>
       <c r="K69" s="35"/>
       <c r="L69" s="4"/>
@@ -5040,8 +5131,8 @@
       <c r="E70" s="33"/>
       <c r="F70" s="35"/>
       <c r="G70" s="35"/>
-      <c r="H70" s="93"/>
-      <c r="I70" s="94"/>
+      <c r="H70" s="259"/>
+      <c r="I70" s="260"/>
       <c r="J70" s="35"/>
       <c r="K70" s="35"/>
       <c r="L70" s="4"/>
@@ -5070,8 +5161,8 @@
       <c r="E72" s="65"/>
       <c r="F72" s="66"/>
       <c r="G72" s="34"/>
-      <c r="H72" s="95"/>
-      <c r="I72" s="95"/>
+      <c r="H72" s="261"/>
+      <c r="I72" s="261"/>
       <c r="J72" s="31"/>
       <c r="K72" s="42"/>
       <c r="L72" s="4"/>
@@ -5085,8 +5176,8 @@
       <c r="E73" s="68"/>
       <c r="F73" s="69"/>
       <c r="G73" s="42"/>
-      <c r="H73" s="96"/>
-      <c r="I73" s="96"/>
+      <c r="H73" s="250"/>
+      <c r="I73" s="250"/>
       <c r="J73" s="31"/>
       <c r="K73" s="31"/>
       <c r="L73" s="4"/>
@@ -5100,8 +5191,8 @@
       <c r="E74" s="71"/>
       <c r="F74" s="72"/>
       <c r="G74" s="72"/>
-      <c r="H74" s="87"/>
-      <c r="I74" s="87"/>
+      <c r="H74" s="264"/>
+      <c r="I74" s="264"/>
       <c r="J74" s="73"/>
       <c r="K74" s="73"/>
       <c r="L74" s="4"/>
@@ -5115,8 +5206,8 @@
       <c r="E75" s="75"/>
       <c r="F75" s="75"/>
       <c r="G75" s="75"/>
-      <c r="H75" s="88"/>
-      <c r="I75" s="89"/>
+      <c r="H75" s="265"/>
+      <c r="I75" s="266"/>
       <c r="J75" s="76"/>
       <c r="K75" s="75"/>
       <c r="L75" s="4"/>
@@ -5130,8 +5221,8 @@
       <c r="E76" s="29"/>
       <c r="F76" s="29"/>
       <c r="G76" s="29"/>
-      <c r="H76" s="85"/>
-      <c r="I76" s="86"/>
+      <c r="H76" s="262"/>
+      <c r="I76" s="263"/>
       <c r="J76" s="78"/>
       <c r="K76" s="29"/>
       <c r="L76" s="4"/>
@@ -5145,8 +5236,8 @@
       <c r="E77" s="35"/>
       <c r="F77" s="35"/>
       <c r="G77" s="35"/>
-      <c r="H77" s="90"/>
-      <c r="I77" s="90"/>
+      <c r="H77" s="267"/>
+      <c r="I77" s="267"/>
       <c r="J77" s="79"/>
       <c r="K77" s="35"/>
       <c r="L77" s="4"/>
@@ -5160,8 +5251,8 @@
       <c r="E78" s="29"/>
       <c r="F78" s="29"/>
       <c r="G78" s="29"/>
-      <c r="H78" s="85"/>
-      <c r="I78" s="86"/>
+      <c r="H78" s="262"/>
+      <c r="I78" s="263"/>
       <c r="J78" s="78"/>
       <c r="K78" s="81"/>
       <c r="L78" s="4"/>
@@ -5175,8 +5266,8 @@
       <c r="E79" s="29"/>
       <c r="F79" s="29"/>
       <c r="G79" s="29"/>
-      <c r="H79" s="85"/>
-      <c r="I79" s="86"/>
+      <c r="H79" s="262"/>
+      <c r="I79" s="263"/>
       <c r="J79" s="78"/>
       <c r="K79" s="81"/>
       <c r="L79" s="83"/>
@@ -5190,8 +5281,8 @@
       <c r="E80" s="29"/>
       <c r="F80" s="29"/>
       <c r="G80" s="29"/>
-      <c r="H80" s="85"/>
-      <c r="I80" s="86"/>
+      <c r="H80" s="262"/>
+      <c r="I80" s="263"/>
       <c r="J80" s="78"/>
       <c r="K80" s="81"/>
       <c r="L80" s="83"/>
@@ -5205,8 +5296,8 @@
       <c r="E81" s="29"/>
       <c r="F81" s="29"/>
       <c r="G81" s="29"/>
-      <c r="H81" s="85"/>
-      <c r="I81" s="86"/>
+      <c r="H81" s="262"/>
+      <c r="I81" s="263"/>
       <c r="J81" s="78"/>
       <c r="K81" s="81"/>
       <c r="L81" s="4"/>
@@ -5307,14 +5398,76 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H27:I27"/>
     <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H44:I44"/>
     <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="J7:K7"/>
@@ -5331,76 +5484,14 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="C46:G46"/>
     <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
